--- a/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
+++ b/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18600" windowHeight="6350"/>
+    <workbookView windowWidth="19200" windowHeight="6800"/>
   </bookViews>
   <sheets>
     <sheet name="Presenças" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="58">
   <si>
     <t>REGISTO DE PRESENÇAS</t>
   </si>
@@ -2342,8 +2342,12 @@
       </c>
       <c r="E9" s="19"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
+      <c r="G9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>19</v>
+      </c>
       <c r="I9" s="19"/>
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
@@ -2399,9 +2403,15 @@
       <c r="F10" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
+      <c r="G10" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="J10" s="27"/>
       <c r="K10" s="27"/>
       <c r="L10" s="27"/>
@@ -2452,9 +2462,15 @@
       </c>
       <c r="E11" s="27"/>
       <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
+      <c r="G11" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="J11" s="27"/>
       <c r="K11" s="27"/>
       <c r="L11" s="27"/>
@@ -2509,9 +2525,15 @@
       <c r="F12" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
+      <c r="G12" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="J12" s="27"/>
       <c r="K12" s="27"/>
       <c r="L12" s="27"/>
@@ -2562,8 +2584,12 @@
       </c>
       <c r="E13" s="27"/>
       <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
+      <c r="G13" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I13" s="27"/>
       <c r="J13" s="27"/>
       <c r="K13" s="27"/>
@@ -2615,8 +2641,12 @@
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
+      <c r="G14" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I14" s="27"/>
       <c r="J14" s="27"/>
       <c r="K14" s="27"/>
@@ -2672,9 +2702,15 @@
       <c r="F15" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
+      <c r="G15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="J15" s="27"/>
       <c r="K15" s="27"/>
       <c r="L15" s="27"/>
@@ -2729,9 +2765,15 @@
       <c r="F16" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
+      <c r="G16" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="J16" s="27"/>
       <c r="K16" s="27"/>
       <c r="L16" s="27"/>
@@ -2786,9 +2828,15 @@
       <c r="F17" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
+      <c r="G17" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="J17" s="27"/>
       <c r="K17" s="27"/>
       <c r="L17" s="27"/>
@@ -2843,9 +2891,15 @@
       <c r="F18" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
+      <c r="G18" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="J18" s="27"/>
       <c r="K18" s="27"/>
       <c r="L18" s="27"/>
@@ -2896,8 +2950,12 @@
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
+      <c r="G19" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I19" s="27"/>
       <c r="J19" s="27"/>
       <c r="K19" s="27"/>
@@ -2953,8 +3011,12 @@
       <c r="F20" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
+      <c r="G20" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I20" s="27"/>
       <c r="J20" s="27"/>
       <c r="K20" s="27"/>
@@ -3010,9 +3072,15 @@
       <c r="F21" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
+      <c r="G21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="J21" s="27"/>
       <c r="K21" s="27"/>
       <c r="L21" s="27"/>
@@ -3067,9 +3135,15 @@
       <c r="F22" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
+      <c r="G22" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="J22" s="27"/>
       <c r="K22" s="27"/>
       <c r="L22" s="27"/>
@@ -3122,8 +3196,12 @@
         <v>19</v>
       </c>
       <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
+      <c r="G23" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I23" s="27"/>
       <c r="J23" s="27"/>
       <c r="K23" s="27"/>
@@ -3179,9 +3257,15 @@
       <c r="F24" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
+      <c r="G24" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="J24" s="27"/>
       <c r="K24" s="27"/>
       <c r="L24" s="27"/>
@@ -3236,9 +3320,15 @@
       <c r="F25" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
+      <c r="G25" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="J25" s="27"/>
       <c r="K25" s="27"/>
       <c r="L25" s="27"/>
@@ -3293,9 +3383,15 @@
       <c r="F26" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
+      <c r="G26" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="36" t="s">
+        <v>19</v>
+      </c>
       <c r="J26" s="36"/>
       <c r="K26" s="36"/>
       <c r="L26" s="36"/>
@@ -3390,15 +3486,15 @@
       </c>
       <c r="G28" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H28" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I28" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J28" s="42">
         <f t="shared" si="3"/>
@@ -3736,7 +3832,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C9:AE26">
+    <dataValidation type="list" sqref="G9:G26 H11:H26 C9:F10 H9:AE10 C11:F26 I11:AE26">
       <formula1>"P,F,J"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
+++ b/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="58">
   <si>
     <t>REGISTO DE PRESENÇAS</t>
   </si>
@@ -1435,11 +1435,11 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="FF14583B"/>
+        <color rgb="FF285785"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFDCF2E8"/>
+          <bgColor rgb="FFDEEDFA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1457,11 +1457,11 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="FF285785"/>
+        <color rgb="FF14583B"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFDEEDFA"/>
+          <bgColor rgb="FFDCF2E8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2345,9 +2345,7 @@
       <c r="G9" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="19" t="s">
-        <v>19</v>
-      </c>
+      <c r="H9" s="19"/>
       <c r="I9" s="19"/>
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
@@ -2462,12 +2460,10 @@
       </c>
       <c r="E11" s="27"/>
       <c r="F11" s="27"/>
-      <c r="G11" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="27" t="s">
-        <v>19</v>
-      </c>
+      <c r="G11" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="27"/>
       <c r="I11" s="27" t="s">
         <v>19</v>
       </c>
@@ -2584,12 +2580,8 @@
       </c>
       <c r="E13" s="27"/>
       <c r="F13" s="27"/>
-      <c r="G13" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="27" t="s">
-        <v>19</v>
-      </c>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
       <c r="I13" s="27"/>
       <c r="J13" s="27"/>
       <c r="K13" s="27"/>
@@ -2641,12 +2633,8 @@
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="27"/>
-      <c r="G14" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="27" t="s">
-        <v>19</v>
-      </c>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
       <c r="I14" s="27"/>
       <c r="J14" s="27"/>
       <c r="K14" s="27"/>
@@ -2702,7 +2690,7 @@
       <c r="F15" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="27" t="s">
         <v>19</v>
       </c>
       <c r="H15" s="27" t="s">
@@ -2828,7 +2816,7 @@
       <c r="F17" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="27" t="s">
         <v>19</v>
       </c>
       <c r="H17" s="27" t="s">
@@ -2950,12 +2938,8 @@
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="27" t="s">
-        <v>19</v>
-      </c>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
       <c r="I19" s="27"/>
       <c r="J19" s="27"/>
       <c r="K19" s="27"/>
@@ -3014,9 +2998,7 @@
       <c r="G20" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="27" t="s">
-        <v>19</v>
-      </c>
+      <c r="H20" s="27"/>
       <c r="I20" s="27"/>
       <c r="J20" s="27"/>
       <c r="K20" s="27"/>
@@ -3072,7 +3054,7 @@
       <c r="F21" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="27" t="s">
         <v>19</v>
       </c>
       <c r="H21" s="27" t="s">
@@ -3196,12 +3178,10 @@
         <v>19</v>
       </c>
       <c r="F23" s="27"/>
-      <c r="G23" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="27" t="s">
-        <v>19</v>
-      </c>
+      <c r="G23" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="27"/>
       <c r="I23" s="27"/>
       <c r="J23" s="27"/>
       <c r="K23" s="27"/>
@@ -3320,7 +3300,7 @@
       <c r="F25" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="27" t="s">
         <v>19</v>
       </c>
       <c r="H25" s="27" t="s">
@@ -3383,10 +3363,10 @@
       <c r="F26" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="G26" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="27" t="s">
+      <c r="G26" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" s="36" t="s">
         <v>19</v>
       </c>
       <c r="I26" s="36" t="s">
@@ -3486,11 +3466,11 @@
       </c>
       <c r="G28" s="42">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H28" s="42">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I28" s="42">
         <f t="shared" si="3"/>
@@ -3820,19 +3800,30 @@
       <c r="AH34" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C9:AE26">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="I9:I26">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>I9="J"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>I9="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>I9="P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:H26;J9:AE26">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>C9="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>C9="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>C9="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G9:G26 H11:H26 C9:F10 H9:AE10 C11:F26 I11:AE26">
+    <dataValidation type="list" sqref="I9:I26 C9:H26 J9:AE26">
       <formula1>"P,F,J"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
+++ b/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="58">
   <si>
     <t>REGISTO DE PRESENÇAS</t>
   </si>
@@ -2347,7 +2347,9 @@
       </c>
       <c r="H9" s="19"/>
       <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
+      <c r="J9" s="19" t="s">
+        <v>19</v>
+      </c>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
@@ -2410,7 +2412,9 @@
       <c r="I10" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="27"/>
+      <c r="J10" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="K10" s="27"/>
       <c r="L10" s="27"/>
       <c r="M10" s="27"/>
@@ -2467,7 +2471,9 @@
       <c r="I11" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="27"/>
+      <c r="J11" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="K11" s="27"/>
       <c r="L11" s="27"/>
       <c r="M11" s="27"/>
@@ -2530,7 +2536,9 @@
       <c r="I12" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="27"/>
+      <c r="J12" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="K12" s="27"/>
       <c r="L12" s="27"/>
       <c r="M12" s="27"/>
@@ -2699,7 +2707,9 @@
       <c r="I15" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="27"/>
+      <c r="J15" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="K15" s="27"/>
       <c r="L15" s="27"/>
       <c r="M15" s="27"/>
@@ -2762,7 +2772,9 @@
       <c r="I16" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="27"/>
+      <c r="J16" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="K16" s="27"/>
       <c r="L16" s="27"/>
       <c r="M16" s="27"/>
@@ -2825,7 +2837,9 @@
       <c r="I17" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="27"/>
+      <c r="J17" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="K17" s="27"/>
       <c r="L17" s="27"/>
       <c r="M17" s="27"/>
@@ -2888,7 +2902,9 @@
       <c r="I18" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J18" s="27"/>
+      <c r="J18" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="K18" s="27"/>
       <c r="L18" s="27"/>
       <c r="M18" s="27"/>
@@ -3063,7 +3079,9 @@
       <c r="I21" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="27"/>
+      <c r="J21" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="K21" s="27"/>
       <c r="L21" s="27"/>
       <c r="M21" s="27"/>
@@ -3126,7 +3144,9 @@
       <c r="I22" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J22" s="27"/>
+      <c r="J22" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="K22" s="27"/>
       <c r="L22" s="27"/>
       <c r="M22" s="27"/>
@@ -3246,7 +3266,9 @@
       <c r="I24" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J24" s="27"/>
+      <c r="J24" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="K24" s="27"/>
       <c r="L24" s="27"/>
       <c r="M24" s="27"/>
@@ -3309,7 +3331,9 @@
       <c r="I25" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="27"/>
+      <c r="J25" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="K25" s="27"/>
       <c r="L25" s="27"/>
       <c r="M25" s="27"/>
@@ -3372,7 +3396,9 @@
       <c r="I26" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="J26" s="36"/>
+      <c r="J26" s="36" t="s">
+        <v>19</v>
+      </c>
       <c r="K26" s="36"/>
       <c r="L26" s="36"/>
       <c r="M26" s="36"/>
@@ -3478,7 +3504,7 @@
       </c>
       <c r="J28" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K28" s="42">
         <f t="shared" si="3"/>
@@ -3823,7 +3849,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="I9:I26 C9:H26 J9:AE26">
+    <dataValidation type="list" sqref="C9:AE26">
       <formula1>"P,F,J"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
+++ b/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="58">
   <si>
     <t>REGISTO DE PRESENÇAS</t>
   </si>
@@ -2350,7 +2350,9 @@
       <c r="J9" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="19"/>
+      <c r="K9" s="19" t="s">
+        <v>19</v>
+      </c>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
@@ -2415,7 +2417,9 @@
       <c r="J10" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="27"/>
+      <c r="K10" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="L10" s="27"/>
       <c r="M10" s="27"/>
       <c r="N10" s="27"/>
@@ -2474,7 +2478,9 @@
       <c r="J11" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="27"/>
+      <c r="K11" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="L11" s="27"/>
       <c r="M11" s="27"/>
       <c r="N11" s="27"/>
@@ -2539,7 +2545,9 @@
       <c r="J12" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="27"/>
+      <c r="K12" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="L12" s="27"/>
       <c r="M12" s="27"/>
       <c r="N12" s="27"/>
@@ -2710,7 +2718,9 @@
       <c r="J15" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="27"/>
+      <c r="K15" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="L15" s="27"/>
       <c r="M15" s="27"/>
       <c r="N15" s="27"/>
@@ -2840,7 +2850,9 @@
       <c r="J17" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="27"/>
+      <c r="K17" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="L17" s="27"/>
       <c r="M17" s="27"/>
       <c r="N17" s="27"/>
@@ -2905,7 +2917,9 @@
       <c r="J18" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K18" s="27"/>
+      <c r="K18" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="L18" s="27"/>
       <c r="M18" s="27"/>
       <c r="N18" s="27"/>
@@ -3082,7 +3096,9 @@
       <c r="J21" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K21" s="27"/>
+      <c r="K21" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="L21" s="27"/>
       <c r="M21" s="27"/>
       <c r="N21" s="27"/>
@@ -3147,7 +3163,9 @@
       <c r="J22" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K22" s="27"/>
+      <c r="K22" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="L22" s="27"/>
       <c r="M22" s="27"/>
       <c r="N22" s="27"/>
@@ -3269,7 +3287,9 @@
       <c r="J24" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K24" s="27"/>
+      <c r="K24" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="L24" s="27"/>
       <c r="M24" s="27"/>
       <c r="N24" s="27"/>
@@ -3334,7 +3354,9 @@
       <c r="J25" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K25" s="27"/>
+      <c r="K25" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="L25" s="27"/>
       <c r="M25" s="27"/>
       <c r="N25" s="27"/>
@@ -3399,7 +3421,9 @@
       <c r="J26" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="K26" s="36"/>
+      <c r="K26" s="36" t="s">
+        <v>19</v>
+      </c>
       <c r="L26" s="36"/>
       <c r="M26" s="36"/>
       <c r="N26" s="36"/>
@@ -3508,7 +3532,7 @@
       </c>
       <c r="K28" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L28" s="42">
         <f t="shared" si="3"/>

--- a/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
+++ b/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="58">
   <si>
     <t>REGISTO DE PRESENÇAS</t>
   </si>
@@ -2353,7 +2353,9 @@
       <c r="K9" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="19"/>
+      <c r="L9" s="19" t="s">
+        <v>19</v>
+      </c>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
       <c r="O9" s="19"/>
@@ -2481,7 +2483,9 @@
       <c r="K11" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L11" s="27"/>
+      <c r="L11" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="M11" s="27"/>
       <c r="N11" s="27"/>
       <c r="O11" s="27"/>
@@ -2548,7 +2552,9 @@
       <c r="K12" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L12" s="27"/>
+      <c r="L12" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="M12" s="27"/>
       <c r="N12" s="27"/>
       <c r="O12" s="27"/>
@@ -2721,7 +2727,9 @@
       <c r="K15" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L15" s="27"/>
+      <c r="L15" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="M15" s="27"/>
       <c r="N15" s="27"/>
       <c r="O15" s="27"/>
@@ -2920,7 +2928,9 @@
       <c r="K18" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L18" s="27"/>
+      <c r="L18" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="M18" s="27"/>
       <c r="N18" s="27"/>
       <c r="O18" s="27"/>
@@ -3166,7 +3176,9 @@
       <c r="K22" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L22" s="27"/>
+      <c r="L22" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="M22" s="27"/>
       <c r="N22" s="27"/>
       <c r="O22" s="27"/>
@@ -3357,7 +3369,9 @@
       <c r="K25" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L25" s="27"/>
+      <c r="L25" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="M25" s="27"/>
       <c r="N25" s="27"/>
       <c r="O25" s="27"/>
@@ -3536,7 +3550,7 @@
       </c>
       <c r="L28" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M28" s="42">
         <f t="shared" si="3"/>

--- a/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
+++ b/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800"/>
+    <workbookView windowWidth="19200" windowHeight="6880"/>
   </bookViews>
   <sheets>
     <sheet name="Presenças" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="61">
   <si>
     <t>REGISTO DE PRESENÇAS</t>
   </si>
@@ -189,6 +189,15 @@
   </si>
   <si>
     <t>Walter Gabriel Souza e Silva</t>
+  </si>
+  <si>
+    <t>Rui Mário José Calado Pires</t>
+  </si>
+  <si>
+    <t>Diogo Miguel Botellero Rodrigues</t>
+  </si>
+  <si>
+    <t>Fernando André Iglésias da Silva</t>
   </si>
   <si>
     <t>Registos por aula</t>
@@ -681,7 +690,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -906,17 +915,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFDCE5E9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB8C8CF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFE8E5DB"/>
       </left>
@@ -1118,7 +1116,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="26" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="25" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1130,34 +1128,34 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1242,7 +1240,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1337,22 +1335,13 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1361,13 +1350,19 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1884,7 +1879,7 @@
   <sheetPr>
     <tabColor rgb="FF173F56"/>
   </sheetPr>
-  <dimension ref="A1:AH34"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2456,10 +2451,10 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:34">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="17" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="18" t="s">
@@ -2588,10 +2583,10 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:34">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="17" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="18" t="s">
@@ -2694,10 +2689,10 @@
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:34">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="17" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="18" t="s">
@@ -2828,10 +2823,10 @@
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:34">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="17" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="18" t="s">
@@ -2964,10 +2959,10 @@
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:34">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="17" t="s">
         <v>39</v>
       </c>
       <c r="C19" s="18" t="s">
@@ -3076,10 +3071,10 @@
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:34">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="18" t="s">
@@ -3212,10 +3207,10 @@
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:34">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="17" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="18" t="s">
@@ -3336,10 +3331,10 @@
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:34">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="17" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="18" t="s">
@@ -3405,10 +3400,10 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:34">
-      <c r="A26" s="34" t="s">
+      <c r="A26" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="25" t="s">
         <v>53</v>
       </c>
       <c r="C26" s="26" t="s">
@@ -3417,281 +3412,269 @@
       <c r="D26" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="I26" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="J26" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="K26" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="36"/>
-      <c r="S26" s="36"/>
-      <c r="T26" s="36"/>
-      <c r="U26" s="36"/>
-      <c r="V26" s="36"/>
-      <c r="W26" s="36"/>
-      <c r="X26" s="36"/>
-      <c r="Y26" s="36"/>
-      <c r="Z26" s="36"/>
-      <c r="AA26" s="36"/>
-      <c r="AB26" s="36"/>
-      <c r="AC26" s="36"/>
-      <c r="AD26" s="36"/>
-      <c r="AE26" s="37"/>
-      <c r="AF26" s="38">
+      <c r="E26" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="33"/>
+      <c r="AF26" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AG26" s="39">
+      <c r="AG26" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH26" s="40">
+      <c r="AH26" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="9" customHeight="1" spans="1:34">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
-      <c r="AD27" s="1"/>
-      <c r="AE27" s="1"/>
-      <c r="AF27" s="1"/>
-      <c r="AG27" s="1"/>
-      <c r="AH27" s="1"/>
+    <row r="27" ht="18" customHeight="1" spans="1:34">
+      <c r="A27" s="16"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="L27" s="32"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="37"/>
+      <c r="P27" s="37"/>
+      <c r="Q27" s="37"/>
+      <c r="R27" s="37"/>
+      <c r="S27" s="37"/>
+      <c r="T27" s="37"/>
+      <c r="U27" s="37"/>
+      <c r="V27" s="37"/>
+      <c r="W27" s="37"/>
+      <c r="X27" s="37"/>
+      <c r="Y27" s="37"/>
+      <c r="Z27" s="37"/>
+      <c r="AA27" s="37"/>
+      <c r="AB27" s="37"/>
+      <c r="AC27" s="37"/>
+      <c r="AD27" s="37"/>
+      <c r="AE27" s="38"/>
+      <c r="AF27" s="39"/>
+      <c r="AG27" s="37"/>
+      <c r="AH27" s="38"/>
     </row>
-    <row r="28" ht="26" customHeight="1" spans="1:34">
-      <c r="A28" s="41"/>
-      <c r="B28" s="41" t="s">
+    <row r="28" customHeight="1" spans="1:34">
+      <c r="A28" s="24">
+        <v>889221</v>
+      </c>
+      <c r="B28" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="42">
-        <f>COUNTIF(C9:C26,"X")+COUNTIF(C9:C26,"F")+COUNTIF(C9:C26,"J")</f>
-        <v>18</v>
-      </c>
-      <c r="D28" s="42">
-        <f t="shared" ref="D28:AH28" si="3">COUNTIF(D9:D26,"X")+COUNTIF(D9:D26,"F")+COUNTIF(D9:D26,"J")</f>
-        <v>18</v>
-      </c>
-      <c r="E28" s="42">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="F28" s="42">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="G28" s="42">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="H28" s="42">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="I28" s="42">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="J28" s="42">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="K28" s="42">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="L28" s="42">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="M28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AB28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AD28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AE28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AF28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH28" s="42">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="C28" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K28" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="L28" s="32"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
+      <c r="O28" s="37"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="37"/>
+      <c r="S28" s="37"/>
+      <c r="T28" s="37"/>
+      <c r="U28" s="37"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="37"/>
+      <c r="Y28" s="37"/>
+      <c r="Z28" s="37"/>
+      <c r="AA28" s="37"/>
+      <c r="AB28" s="37"/>
+      <c r="AC28" s="37"/>
+      <c r="AD28" s="37"/>
+      <c r="AE28" s="38"/>
+      <c r="AF28" s="39"/>
+      <c r="AG28" s="37"/>
+      <c r="AH28" s="38"/>
     </row>
-    <row r="29" ht="12" customHeight="1" spans="1:34">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
-      <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
-      <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
-      <c r="AF29" s="1"/>
-      <c r="AG29" s="1"/>
-      <c r="AH29" s="1"/>
+    <row r="29" ht="19" customHeight="1" spans="1:34">
+      <c r="A29" s="16">
+        <v>13907</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="L29" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="M29" s="37"/>
+      <c r="N29" s="37"/>
+      <c r="O29" s="37"/>
+      <c r="P29" s="37"/>
+      <c r="Q29" s="37"/>
+      <c r="R29" s="37"/>
+      <c r="S29" s="37"/>
+      <c r="T29" s="37"/>
+      <c r="U29" s="37"/>
+      <c r="V29" s="37"/>
+      <c r="W29" s="37"/>
+      <c r="X29" s="37"/>
+      <c r="Y29" s="37"/>
+      <c r="Z29" s="37"/>
+      <c r="AA29" s="37"/>
+      <c r="AB29" s="37"/>
+      <c r="AC29" s="37"/>
+      <c r="AD29" s="37"/>
+      <c r="AE29" s="38"/>
+      <c r="AF29" s="39"/>
+      <c r="AG29" s="37"/>
+      <c r="AH29" s="38"/>
     </row>
-    <row r="30" ht="20" customHeight="1" spans="1:34">
-      <c r="A30" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+    <row r="30" ht="21" customHeight="1" spans="1:34">
+      <c r="A30" s="24">
+        <v>13906</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="L30" s="32" t="s">
+        <v>19</v>
+      </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
@@ -3715,48 +3698,142 @@
       <c r="AG30" s="1"/>
       <c r="AH30" s="1"/>
     </row>
-    <row r="31" ht="20" customHeight="1" spans="1:34">
-      <c r="A31" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
-      <c r="AB31" s="1"/>
-      <c r="AC31" s="1"/>
-      <c r="AD31" s="1"/>
-      <c r="AE31" s="1"/>
-      <c r="AF31" s="1"/>
-      <c r="AG31" s="1"/>
-      <c r="AH31" s="1"/>
+    <row r="31" ht="26" customHeight="1" spans="1:34">
+      <c r="A31" s="40"/>
+      <c r="B31" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="41">
+        <f>COUNTIF(C9:C26,"X")+COUNTIF(C9:C26,"F")+COUNTIF(C9:C26,"J")</f>
+        <v>18</v>
+      </c>
+      <c r="D31" s="41">
+        <f t="shared" ref="D31:AH31" si="3">COUNTIF(D9:D26,"X")+COUNTIF(D9:D26,"F")+COUNTIF(D9:D26,"J")</f>
+        <v>18</v>
+      </c>
+      <c r="E31" s="41">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="F31" s="41">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="G31" s="41">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="H31" s="41">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="I31" s="41">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="J31" s="41">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="K31" s="41">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="L31" s="41">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="M31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH31" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" ht="20" customHeight="1" spans="1:34">
-      <c r="A32" s="45" t="s">
-        <v>57</v>
-      </c>
+    <row r="32" ht="12" customHeight="1" spans="1:34">
+      <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -3791,8 +3868,10 @@
       <c r="AG32" s="1"/>
       <c r="AH32" s="1"/>
     </row>
-    <row r="33" spans="1:34">
-      <c r="A33" s="1"/>
+    <row r="33" ht="20" customHeight="1" spans="1:34">
+      <c r="A33" s="42" t="s">
+        <v>58</v>
+      </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -3827,8 +3906,10 @@
       <c r="AG33" s="1"/>
       <c r="AH33" s="1"/>
     </row>
-    <row r="34" spans="1:34">
-      <c r="A34" s="1"/>
+    <row r="34" ht="20" customHeight="1" spans="1:34">
+      <c r="A34" s="43" t="s">
+        <v>59</v>
+      </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -3863,31 +3944,240 @@
       <c r="AG34" s="1"/>
       <c r="AH34" s="1"/>
     </row>
+    <row r="35" ht="20" customHeight="1" spans="1:34">
+      <c r="A35" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1"/>
+      <c r="AG35" s="1"/>
+      <c r="AH35" s="1"/>
+    </row>
+    <row r="36" spans="1:34">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1"/>
+      <c r="AH36" s="1"/>
+    </row>
+    <row r="37" spans="1:34">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1"/>
+      <c r="AF37" s="1"/>
+      <c r="AG37" s="1"/>
+      <c r="AH37" s="1"/>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="I27">
+    <cfRule type="expression" dxfId="0" priority="24">
+      <formula>I27="J"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="23">
+      <formula>I27="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="22">
+      <formula>I27="P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I28">
+    <cfRule type="expression" dxfId="0" priority="18">
+      <formula>I28="J"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="17">
+      <formula>I28="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="16">
+      <formula>I28="P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29">
+    <cfRule type="expression" dxfId="0" priority="12">
+      <formula>I29="J"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="11">
+      <formula>I29="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="10">
+      <formula>I29="P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I30">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>I30="J"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>I30="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>I30="P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L30">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>L30="J"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>L30="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>L30="P"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I9:I26">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="2" priority="28">
+      <formula>I9="P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="29">
+      <formula>I9="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>I9="J"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>I9="F"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>I9="P"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:H26;J9:AE26">
-    <cfRule type="expression" dxfId="2" priority="4">
+  <conditionalFormatting sqref="C9:H26;J9:AE26;M27:AE29">
+    <cfRule type="expression" dxfId="2" priority="31">
       <formula>C9="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="1" priority="32">
       <formula>C9="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="33">
       <formula>C9="J"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C27:H27;J27:L27">
+    <cfRule type="expression" dxfId="0" priority="27">
+      <formula>C27="J"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="26">
+      <formula>C27="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="25">
+      <formula>C27="P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C28:H28;J28:L28">
+    <cfRule type="expression" dxfId="0" priority="21">
+      <formula>C28="J"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="20">
+      <formula>C28="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="19">
+      <formula>C28="P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29:H29;J29:L29">
+    <cfRule type="expression" dxfId="0" priority="15">
+      <formula>C29="J"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="14">
+      <formula>C29="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="13">
+      <formula>C29="P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C30:H30;J30:K30">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>C30="J"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="8">
+      <formula>C30="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="7">
+      <formula>C30="P"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C9:AE26">
+    <dataValidation type="list" sqref="C27:L27 C28:L28 C29:L29 C30:K30 L30 C9:AE26">
       <formula1>"P,F,J"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
+++ b/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6880"/>
+    <workbookView windowWidth="19200" windowHeight="6800"/>
   </bookViews>
   <sheets>
     <sheet name="Presenças" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="61">
   <si>
     <t>REGISTO DE PRESENÇAS</t>
   </si>
@@ -1240,7 +1240,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1349,15 +1349,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1430,11 +1421,11 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="FF285785"/>
+        <color rgb="FF14583B"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFDEEDFA"/>
+          <bgColor rgb="FFDCF2E8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1452,11 +1443,11 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="FF14583B"/>
+        <color rgb="FF285785"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFDCF2E8"/>
+          <bgColor rgb="FFDEEDFA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1879,7 +1870,7 @@
   <sheetPr>
     <tabColor rgb="FF173F56"/>
   </sheetPr>
-  <dimension ref="A1:AH37"/>
+  <dimension ref="A1:AH36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2351,7 +2342,9 @@
       <c r="L9" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="19"/>
+      <c r="M9" s="19" t="s">
+        <v>19</v>
+      </c>
       <c r="N9" s="19"/>
       <c r="O9" s="19"/>
       <c r="P9" s="19"/>
@@ -2418,7 +2411,9 @@
         <v>19</v>
       </c>
       <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
+      <c r="M10" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="N10" s="27"/>
       <c r="O10" s="27"/>
       <c r="P10" s="27"/>
@@ -2481,7 +2476,9 @@
       <c r="L11" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="M11" s="27"/>
+      <c r="M11" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="N11" s="27"/>
       <c r="O11" s="27"/>
       <c r="P11" s="27"/>
@@ -2725,7 +2722,9 @@
       <c r="L15" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="M15" s="27"/>
+      <c r="M15" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="N15" s="27"/>
       <c r="O15" s="27"/>
       <c r="P15" s="27"/>
@@ -2790,7 +2789,9 @@
       </c>
       <c r="K16" s="27"/>
       <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
+      <c r="M16" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="N16" s="27"/>
       <c r="O16" s="27"/>
       <c r="P16" s="27"/>
@@ -2857,7 +2858,9 @@
         <v>19</v>
       </c>
       <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
+      <c r="M17" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="N17" s="27"/>
       <c r="O17" s="27"/>
       <c r="P17" s="27"/>
@@ -3105,7 +3108,9 @@
         <v>19</v>
       </c>
       <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
+      <c r="M21" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="N21" s="27"/>
       <c r="O21" s="27"/>
       <c r="P21" s="27"/>
@@ -3174,7 +3179,9 @@
       <c r="L22" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="M22" s="27"/>
+      <c r="M22" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="N22" s="27"/>
       <c r="O22" s="27"/>
       <c r="P22" s="27"/>
@@ -3367,7 +3374,9 @@
       <c r="L25" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="M25" s="27"/>
+      <c r="M25" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="N25" s="27"/>
       <c r="O25" s="27"/>
       <c r="P25" s="27"/>
@@ -3434,7 +3443,9 @@
         <v>19</v>
       </c>
       <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
+      <c r="M26" s="32" t="s">
+        <v>19</v>
+      </c>
       <c r="N26" s="32"/>
       <c r="O26" s="32"/>
       <c r="P26" s="32"/>
@@ -3466,9 +3477,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1" spans="1:34">
-      <c r="A27" s="16"/>
-      <c r="B27" s="17"/>
+    <row r="27" customHeight="1" spans="1:34">
+      <c r="A27" s="24">
+        <v>889221</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>54</v>
+      </c>
       <c r="C27" s="26" t="s">
         <v>19</v>
       </c>
@@ -3496,36 +3511,40 @@
       <c r="K27" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="L27" s="32"/>
-      <c r="M27" s="37"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="37"/>
-      <c r="P27" s="37"/>
-      <c r="Q27" s="37"/>
-      <c r="R27" s="37"/>
-      <c r="S27" s="37"/>
-      <c r="T27" s="37"/>
-      <c r="U27" s="37"/>
-      <c r="V27" s="37"/>
-      <c r="W27" s="37"/>
-      <c r="X27" s="37"/>
-      <c r="Y27" s="37"/>
-      <c r="Z27" s="37"/>
-      <c r="AA27" s="37"/>
-      <c r="AB27" s="37"/>
-      <c r="AC27" s="37"/>
-      <c r="AD27" s="37"/>
-      <c r="AE27" s="38"/>
-      <c r="AF27" s="39"/>
-      <c r="AG27" s="37"/>
-      <c r="AH27" s="38"/>
+      <c r="L27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1"/>
+      <c r="AG27" s="1"/>
+      <c r="AH27" s="1"/>
     </row>
-    <row r="28" customHeight="1" spans="1:34">
-      <c r="A28" s="24">
-        <v>889221</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>54</v>
+    <row r="28" ht="19" customHeight="1" spans="1:34">
+      <c r="A28" s="16">
+        <v>13907</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="C28" s="26" t="s">
         <v>19</v>
@@ -3554,36 +3573,40 @@
       <c r="K28" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="L28" s="32"/>
-      <c r="M28" s="37"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="P28" s="37"/>
-      <c r="Q28" s="37"/>
-      <c r="R28" s="37"/>
-      <c r="S28" s="37"/>
-      <c r="T28" s="37"/>
-      <c r="U28" s="37"/>
-      <c r="V28" s="37"/>
-      <c r="W28" s="37"/>
-      <c r="X28" s="37"/>
-      <c r="Y28" s="37"/>
-      <c r="Z28" s="37"/>
-      <c r="AA28" s="37"/>
-      <c r="AB28" s="37"/>
-      <c r="AC28" s="37"/>
-      <c r="AD28" s="37"/>
-      <c r="AE28" s="38"/>
-      <c r="AF28" s="39"/>
-      <c r="AG28" s="37"/>
-      <c r="AH28" s="38"/>
+      <c r="L28" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="1"/>
     </row>
-    <row r="29" ht="19" customHeight="1" spans="1:34">
-      <c r="A29" s="16">
-        <v>13907</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>55</v>
+    <row r="29" ht="21" customHeight="1" spans="1:34">
+      <c r="A29" s="24">
+        <v>13906</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>56</v>
       </c>
       <c r="C29" s="26" t="s">
         <v>19</v>
@@ -3615,225 +3638,203 @@
       <c r="L29" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="M29" s="37"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="37"/>
-      <c r="P29" s="37"/>
-      <c r="Q29" s="37"/>
-      <c r="R29" s="37"/>
-      <c r="S29" s="37"/>
-      <c r="T29" s="37"/>
-      <c r="U29" s="37"/>
-      <c r="V29" s="37"/>
-      <c r="W29" s="37"/>
-      <c r="X29" s="37"/>
-      <c r="Y29" s="37"/>
-      <c r="Z29" s="37"/>
-      <c r="AA29" s="37"/>
-      <c r="AB29" s="37"/>
-      <c r="AC29" s="37"/>
-      <c r="AD29" s="37"/>
-      <c r="AE29" s="38"/>
-      <c r="AF29" s="39"/>
-      <c r="AG29" s="37"/>
-      <c r="AH29" s="38"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="1"/>
     </row>
-    <row r="30" ht="21" customHeight="1" spans="1:34">
-      <c r="A30" s="24">
-        <v>13906</v>
-      </c>
-      <c r="B30" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="I30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="K30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="L30" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
-      <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
-      <c r="AF30" s="1"/>
-      <c r="AG30" s="1"/>
-      <c r="AH30" s="1"/>
-    </row>
-    <row r="31" ht="26" customHeight="1" spans="1:34">
-      <c r="A31" s="40"/>
-      <c r="B31" s="40" t="s">
+    <row r="30" ht="26" customHeight="1" spans="1:34">
+      <c r="A30" s="37"/>
+      <c r="B30" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="41">
-        <f>COUNTIF(C9:C26,"X")+COUNTIF(C9:C26,"F")+COUNTIF(C9:C26,"J")</f>
+      <c r="C30" s="38">
+        <f>COUNTIF(C9:C29,"X")+COUNTIF(C9:C29,"F")+COUNTIF(C9:C29,"J")</f>
+        <v>21</v>
+      </c>
+      <c r="D30" s="38">
+        <f t="shared" ref="D30:AH30" si="3">COUNTIF(D9:D29,"X")+COUNTIF(D9:D29,"F")+COUNTIF(D9:D29,"J")</f>
+        <v>21</v>
+      </c>
+      <c r="E30" s="38">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="F30" s="38">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="G30" s="38">
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="D31" s="41">
-        <f t="shared" ref="D31:AH31" si="3">COUNTIF(D9:D26,"X")+COUNTIF(D9:D26,"F")+COUNTIF(D9:D26,"J")</f>
-        <v>18</v>
-      </c>
-      <c r="E31" s="41">
+      <c r="H30" s="38">
         <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="F31" s="41">
+        <v>14</v>
+      </c>
+      <c r="I30" s="38">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="J30" s="38">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="K30" s="38">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="L30" s="38">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="M30" s="38">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="G31" s="41">
+      <c r="N30" s="38">
         <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="H31" s="41">
+        <v>0</v>
+      </c>
+      <c r="O30" s="38">
         <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="I31" s="41">
+        <v>0</v>
+      </c>
+      <c r="P30" s="38">
         <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="J31" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="38">
         <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="K31" s="41">
+        <v>0</v>
+      </c>
+      <c r="R30" s="38">
         <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="L31" s="41">
+        <v>0</v>
+      </c>
+      <c r="S30" s="38">
         <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="M31" s="41">
+        <v>0</v>
+      </c>
+      <c r="T30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N31" s="41">
+      <c r="U30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O31" s="41">
+      <c r="V30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P31" s="41">
+      <c r="W30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="41">
+      <c r="X30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R31" s="41">
+      <c r="Y30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S31" s="41">
+      <c r="Z30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T31" s="41">
+      <c r="AA30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U31" s="41">
+      <c r="AB30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V31" s="41">
+      <c r="AC30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W31" s="41">
+      <c r="AD30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X31" s="41">
+      <c r="AE30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y31" s="41">
+      <c r="AF30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z31" s="41">
+      <c r="AG30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA31" s="41">
+      <c r="AH30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB31" s="41">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC31" s="41">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AD31" s="41">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AE31" s="41">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AF31" s="41">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG31" s="41">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH31" s="41">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="32" ht="12" customHeight="1" spans="1:34">
-      <c r="A32" s="1"/>
+    <row r="31" ht="12" customHeight="1" spans="1:34">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AH31" s="1"/>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="1:34">
+      <c r="A32" s="39" t="s">
+        <v>58</v>
+      </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -3869,8 +3870,8 @@
       <c r="AH32" s="1"/>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:34">
-      <c r="A33" s="42" t="s">
-        <v>58</v>
+      <c r="A33" s="40" t="s">
+        <v>59</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -3907,8 +3908,8 @@
       <c r="AH33" s="1"/>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:34">
-      <c r="A34" s="43" t="s">
-        <v>59</v>
+      <c r="A34" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3944,10 +3945,8 @@
       <c r="AG34" s="1"/>
       <c r="AH34" s="1"/>
     </row>
-    <row r="35" ht="20" customHeight="1" spans="1:34">
-      <c r="A35" s="44" t="s">
-        <v>60</v>
-      </c>
+    <row r="35" spans="1:34">
+      <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -4018,166 +4017,108 @@
       <c r="AG36" s="1"/>
       <c r="AH36" s="1"/>
     </row>
-    <row r="37" spans="1:34">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
-      <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
-      <c r="AD37" s="1"/>
-      <c r="AE37" s="1"/>
-      <c r="AF37" s="1"/>
-      <c r="AG37" s="1"/>
-      <c r="AH37" s="1"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="I27">
-    <cfRule type="expression" dxfId="0" priority="24">
-      <formula>I27="J"</formula>
+    <cfRule type="expression" dxfId="0" priority="16">
+      <formula>I27="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="23">
+    <cfRule type="expression" dxfId="1" priority="17">
       <formula>I27="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="22">
-      <formula>I27="P"</formula>
+    <cfRule type="expression" dxfId="2" priority="18">
+      <formula>I27="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28">
-    <cfRule type="expression" dxfId="0" priority="18">
-      <formula>I28="J"</formula>
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>I28="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="17">
+    <cfRule type="expression" dxfId="1" priority="11">
       <formula>I28="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="16">
-      <formula>I28="P"</formula>
+    <cfRule type="expression" dxfId="2" priority="12">
+      <formula>I28="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>I29="P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>I29="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>I29="J"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="11">
-      <formula>I29="F"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="10">
-      <formula>I29="P"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I30">
-    <cfRule type="expression" dxfId="0" priority="6">
-      <formula>I30="J"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="5">
-      <formula>I30="F"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
-      <formula>I30="P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L30">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>L30="J"</formula>
+  <conditionalFormatting sqref="L29">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>L29="P"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>L30="F"</formula>
+      <formula>L29="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>L30="P"</formula>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>L29="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I26">
-    <cfRule type="expression" dxfId="2" priority="28">
+    <cfRule type="expression" dxfId="0" priority="28">
       <formula>I9="P"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="29">
       <formula>I9="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="2" priority="30">
       <formula>I9="J"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:H26;J9:AE26;M27:AE29">
-    <cfRule type="expression" dxfId="2" priority="31">
+  <conditionalFormatting sqref="C9:H26;J9:AE26;M27:AE28">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>C9="P"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="32">
       <formula>C9="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="2" priority="33">
       <formula>C9="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27:H27;J27:L27">
-    <cfRule type="expression" dxfId="0" priority="27">
-      <formula>C27="J"</formula>
+    <cfRule type="expression" dxfId="0" priority="19">
+      <formula>C27="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="26">
+    <cfRule type="expression" dxfId="1" priority="20">
       <formula>C27="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="25">
-      <formula>C27="P"</formula>
+    <cfRule type="expression" dxfId="2" priority="21">
+      <formula>C27="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:H28;J28:L28">
-    <cfRule type="expression" dxfId="0" priority="21">
+    <cfRule type="expression" dxfId="0" priority="13">
+      <formula>C28="P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="14">
+      <formula>C28="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="15">
       <formula>C28="J"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="20">
-      <formula>C28="F"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29:H29;J29:K29">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>C29="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="19">
-      <formula>C28="P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C29:H29;J29:L29">
-    <cfRule type="expression" dxfId="0" priority="15">
-      <formula>C29="J"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="14">
+    <cfRule type="expression" dxfId="1" priority="8">
       <formula>C29="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="13">
-      <formula>C29="P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C30:H30;J30:K30">
-    <cfRule type="expression" dxfId="0" priority="9">
-      <formula>C30="J"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="8">
-      <formula>C30="F"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="7">
-      <formula>C30="P"</formula>
+    <cfRule type="expression" dxfId="2" priority="9">
+      <formula>C29="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C27:L27 C28:L28 C29:L29 C30:K30 L30 C9:AE26">
+    <dataValidation type="list" sqref="C9:AE26 C27:L29">
       <formula1>"P,F,J"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
+++ b/Folha_de_Presencas_Introducao_a_Programacao_2026-27.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="61">
   <si>
     <t>REGISTO DE PRESENÇAS</t>
   </si>
@@ -2345,7 +2345,9 @@
       <c r="M9" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="19"/>
+      <c r="N9" s="19" t="s">
+        <v>19</v>
+      </c>
       <c r="O9" s="19"/>
       <c r="P9" s="19"/>
       <c r="Q9" s="19"/>
@@ -2414,7 +2416,9 @@
       <c r="M10" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="N10" s="27"/>
+      <c r="N10" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="O10" s="27"/>
       <c r="P10" s="27"/>
       <c r="Q10" s="27"/>
@@ -2479,7 +2483,9 @@
       <c r="M11" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="N11" s="27"/>
+      <c r="N11" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="O11" s="27"/>
       <c r="P11" s="27"/>
       <c r="Q11" s="27"/>
@@ -2725,7 +2731,9 @@
       <c r="M15" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="N15" s="27"/>
+      <c r="N15" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="O15" s="27"/>
       <c r="P15" s="27"/>
       <c r="Q15" s="27"/>
@@ -2792,7 +2800,9 @@
       <c r="M16" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="N16" s="27"/>
+      <c r="N16" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="O16" s="27"/>
       <c r="P16" s="27"/>
       <c r="Q16" s="27"/>
@@ -2861,7 +2871,9 @@
       <c r="M17" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="N17" s="27"/>
+      <c r="N17" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="O17" s="27"/>
       <c r="P17" s="27"/>
       <c r="Q17" s="27"/>
@@ -2930,7 +2942,9 @@
         <v>19</v>
       </c>
       <c r="M18" s="27"/>
-      <c r="N18" s="27"/>
+      <c r="N18" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="O18" s="27"/>
       <c r="P18" s="27"/>
       <c r="Q18" s="27"/>
@@ -3111,7 +3125,9 @@
       <c r="M21" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="N21" s="27"/>
+      <c r="N21" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="O21" s="27"/>
       <c r="P21" s="27"/>
       <c r="Q21" s="27"/>
@@ -3182,7 +3198,9 @@
       <c r="M22" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="N22" s="27"/>
+      <c r="N22" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="O22" s="27"/>
       <c r="P22" s="27"/>
       <c r="Q22" s="27"/>
@@ -3377,7 +3395,9 @@
       <c r="M25" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="N25" s="27"/>
+      <c r="N25" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="O25" s="27"/>
       <c r="P25" s="27"/>
       <c r="Q25" s="27"/>
@@ -3514,27 +3534,29 @@
       <c r="L27" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="M27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
-      <c r="AD27" s="1"/>
-      <c r="AE27" s="1"/>
+      <c r="M27" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="N27" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="27"/>
+      <c r="AD27" s="27"/>
+      <c r="AE27" s="27"/>
       <c r="AF27" s="1"/>
       <c r="AG27" s="1"/>
       <c r="AH27" s="1"/>
@@ -3576,27 +3598,29 @@
       <c r="L28" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="M28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="1"/>
-      <c r="AE28" s="1"/>
+      <c r="M28" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="N28" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
+      <c r="AA28" s="32"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="32"/>
       <c r="AF28" s="1"/>
       <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
@@ -3638,25 +3662,27 @@
       <c r="L29" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
-      <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
-      <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="O29" s="27"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="27"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="27"/>
+      <c r="AA29" s="27"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="27"/>
+      <c r="AD29" s="27"/>
+      <c r="AE29" s="27"/>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
@@ -3712,7 +3738,7 @@
       </c>
       <c r="N30" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O30" s="38">
         <f t="shared" si="3"/>
@@ -4019,101 +4045,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I27">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>I27="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="17">
+    <cfRule type="expression" dxfId="1" priority="20">
       <formula>I27="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="18">
+    <cfRule type="expression" dxfId="2" priority="21">
       <formula>I27="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>I28="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="11">
+    <cfRule type="expression" dxfId="1" priority="14">
       <formula>I28="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="12">
+    <cfRule type="expression" dxfId="2" priority="15">
       <formula>I28="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>I29="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="1" priority="8">
       <formula>I29="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6">
+    <cfRule type="expression" dxfId="2" priority="9">
       <formula>I29="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L29">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>L29="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>L29="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>L29="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I26">
-    <cfRule type="expression" dxfId="0" priority="28">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>I9="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="29">
+    <cfRule type="expression" dxfId="1" priority="32">
       <formula>I9="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="30">
+    <cfRule type="expression" dxfId="2" priority="33">
       <formula>I9="J"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:H26;J9:AE26;M27:AE28">
-    <cfRule type="expression" dxfId="0" priority="31">
+  <conditionalFormatting sqref="C9:H26;J9:AE26">
+    <cfRule type="expression" dxfId="0" priority="34">
       <formula>C9="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="32">
+    <cfRule type="expression" dxfId="1" priority="35">
       <formula>C9="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="33">
+    <cfRule type="expression" dxfId="2" priority="36">
       <formula>C9="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27:H27;J27:L27">
-    <cfRule type="expression" dxfId="0" priority="19">
+    <cfRule type="expression" dxfId="0" priority="22">
       <formula>C27="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="20">
+    <cfRule type="expression" dxfId="1" priority="23">
       <formula>C27="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="21">
+    <cfRule type="expression" dxfId="2" priority="24">
       <formula>C27="J"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M27:AE29">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>M27="J"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>M27="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>M27="P"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C28:H28;J28:L28">
-    <cfRule type="expression" dxfId="0" priority="13">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>C28="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="14">
+    <cfRule type="expression" dxfId="1" priority="17">
       <formula>C28="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="15">
+    <cfRule type="expression" dxfId="2" priority="18">
       <formula>C28="J"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29:H29;J29:K29">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>C29="P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="8">
+    <cfRule type="expression" dxfId="1" priority="11">
       <formula>C29="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="9">
+    <cfRule type="expression" dxfId="2" priority="12">
       <formula>C29="J"</formula>
     </cfRule>
   </conditionalFormatting>
